--- a/EBOOK/ASGL Quotation for shipment 09.01.2026.xlsx
+++ b/EBOOK/ASGL Quotation for shipment 09.01.2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bear1108/Documents/GitHub/5P-SLMS/EBOOK/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919A3279-BDA7-4657-AD0A-2DADEC5F4151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113B570A-8723-454D-883E-71B91636050E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="28920" windowHeight="15600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28920" windowHeight="15600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation" sheetId="25" r:id="rId1"/>
@@ -594,9 +594,6 @@
     <t>Net weight less than 5 ton</t>
   </si>
   <si>
-    <t>Customer's name: Samsung SDS Vietnam Co., Ltd</t>
-  </si>
-  <si>
     <t>Case by case</t>
   </si>
   <si>
@@ -719,6 +716,9 @@
   <si>
     <t>Loading at ASGL 
 (NonContracted)</t>
+  </si>
+  <si>
+    <t>Customer's name: TDI</t>
   </si>
 </sst>
 </file>
@@ -726,8 +726,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="\$#,##0\ ;\(\$#,##0\)"/>
     <numFmt numFmtId="167" formatCode="&quot;\&quot;#,##0;[Red]&quot;\&quot;&quot;\&quot;\-#,##0"/>
@@ -1486,11 +1486,11 @@
   <cellStyleXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1523,7 +1523,7 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1813,7 +1813,7 @@
     <xf numFmtId="165" fontId="36" fillId="10" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="10" borderId="19" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="36" fillId="10" borderId="19" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="172" fontId="36" fillId="10" borderId="19" xfId="30" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1853,105 +1853,6 @@
     <xf numFmtId="165" fontId="25" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="10" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="10" borderId="20" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="29" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="33" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="10" borderId="23" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1964,7 +1865,7 @@
     <xf numFmtId="165" fontId="36" fillId="10" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="10" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="36" fillId="10" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="172" fontId="36" fillId="10" borderId="24" xfId="30" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1977,40 +1878,139 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="36" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="53" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="28" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="36" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="32" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="10" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="10" borderId="20" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="2" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="36" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="33" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="10" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="10" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="32" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="37" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="53" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="28" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="40">
@@ -2511,116 +2511,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I67"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="63.85546875" style="1" customWidth="1"/>
-    <col min="3" max="5" width="31.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="63.83203125" style="1" customWidth="1"/>
+    <col min="3" max="5" width="31.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40.5" customHeight="1">
-      <c r="B1" s="129" t="s">
+      <c r="B1" s="144" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="174"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="137"/>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="175"/>
-      <c r="B2" s="130" t="s">
-        <v>188</v>
-      </c>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="175"/>
+      <c r="A2" s="138"/>
+      <c r="B2" s="145" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="138"/>
     </row>
     <row r="3" spans="1:9" ht="24.75" customHeight="1">
-      <c r="A3" s="173" t="s">
+      <c r="A3" s="149" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
     </row>
     <row r="4" spans="1:9" s="5" customFormat="1" ht="19.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" ht="29.25" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B5" s="34"/>
       <c r="C5" s="34"/>
       <c r="D5" s="34"/>
       <c r="E5" s="34"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="132" t="s">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="A6" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="132"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="150"/>
+      <c r="D6" s="150"/>
+      <c r="E6" s="150"/>
       <c r="F6" s="22"/>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="132" t="s">
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="A7" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="132"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
       <c r="I7" s="22"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="132" t="s">
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="A8" s="150" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
+      <c r="B8" s="150"/>
+      <c r="C8" s="150"/>
+      <c r="D8" s="150"/>
+      <c r="E8" s="150"/>
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="132" t="s">
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="A9" s="150" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="132"/>
-      <c r="E9" s="132"/>
+      <c r="B9" s="150"/>
+      <c r="C9" s="150"/>
+      <c r="D9" s="150"/>
+      <c r="E9" s="150"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
       <c r="I9" s="22"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="127" t="s">
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="A10" s="147" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
-      <c r="D10" s="127"/>
-      <c r="E10" s="127"/>
+      <c r="B10" s="147"/>
+      <c r="C10" s="147"/>
+      <c r="D10" s="147"/>
+      <c r="E10" s="147"/>
       <c r="F10" s="28"/>
       <c r="I10" s="21"/>
     </row>
@@ -2638,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="10" customFormat="1" ht="19.5" customHeight="1">
@@ -2838,13 +2838,13 @@
         <v>6</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="C27" s="136" t="s">
-        <v>159</v>
-      </c>
-      <c r="D27" s="137"/>
-      <c r="E27" s="138"/>
+        <v>160</v>
+      </c>
+      <c r="C27" s="154" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" s="155"/>
+      <c r="E27" s="156"/>
       <c r="F27" s="94"/>
     </row>
     <row r="28" spans="1:6" s="10" customFormat="1" ht="19.5" customHeight="1">
@@ -2939,7 +2939,7 @@
     <row r="35" spans="1:6" s="10" customFormat="1" ht="19.5" customHeight="1">
       <c r="A35" s="30"/>
       <c r="B35" s="35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C35" s="36" t="s">
         <v>33</v>
@@ -3084,10 +3084,10 @@
         <v>13</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D46" s="121">
         <v>4000000</v>
@@ -3185,25 +3185,25 @@
         <v>17</v>
       </c>
       <c r="B53" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C53" s="18" t="s">
         <v>169</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>170</v>
       </c>
       <c r="D53" s="14">
         <v>150000</v>
       </c>
       <c r="E53" s="14"/>
     </row>
-    <row r="54" spans="1:6" s="10" customFormat="1" ht="31.5">
+    <row r="54" spans="1:6" s="10" customFormat="1" ht="34">
       <c r="A54" s="30">
         <v>18</v>
       </c>
       <c r="B54" s="92" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D54" s="17">
         <v>65000</v>
@@ -3211,12 +3211,12 @@
       <c r="E54" s="17"/>
       <c r="F54" s="20"/>
     </row>
-    <row r="55" spans="1:6" s="10" customFormat="1" ht="16.5">
+    <row r="55" spans="1:6" s="10" customFormat="1" ht="17">
       <c r="A55" s="30">
         <v>19</v>
       </c>
       <c r="B55" s="92" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>152</v>
@@ -3227,7 +3227,7 @@
       <c r="E55" s="17"/>
       <c r="F55" s="20"/>
     </row>
-    <row r="56" spans="1:6" s="10" customFormat="1" ht="16.5">
+    <row r="56" spans="1:6" s="10" customFormat="1" ht="17">
       <c r="A56" s="11" t="s">
         <v>10</v>
       </c>
@@ -3245,25 +3245,25 @@
       <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:6" s="10" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A59" s="133"/>
-      <c r="B59" s="134"/>
-      <c r="C59" s="128" t="s">
+      <c r="A59" s="151"/>
+      <c r="B59" s="152"/>
+      <c r="C59" s="148" t="s">
         <v>64</v>
       </c>
-      <c r="D59" s="128"/>
-      <c r="E59" s="128"/>
-    </row>
-    <row r="60" spans="1:6" s="5" customFormat="1" ht="18.75">
-      <c r="C60" s="135"/>
-      <c r="D60" s="135"/>
-      <c r="E60" s="135"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+    </row>
+    <row r="60" spans="1:6" s="5" customFormat="1" ht="18">
+      <c r="C60" s="153"/>
+      <c r="D60" s="153"/>
+      <c r="E60" s="153"/>
     </row>
     <row r="67" spans="3:5">
-      <c r="C67" s="126" t="s">
-        <v>184</v>
-      </c>
-      <c r="D67" s="126"/>
-      <c r="E67" s="126"/>
+      <c r="C67" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="D67" s="146"/>
+      <c r="E67" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -3291,42 +3291,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5255DA00-3B21-4F12-BA75-09EA64788A5D}">
   <dimension ref="A1:I37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="63.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="31.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="43.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="63.83203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="31.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="43.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30.75" customHeight="1">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="144" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A2" s="130" t="s">
-        <v>186</v>
-      </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
+      <c r="A2" s="145" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="145"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="157" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="131"/>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
     </row>
     <row r="4" spans="1:9" s="5" customFormat="1" ht="29.25" customHeight="1">
       <c r="A4" s="3" t="s">
@@ -3336,73 +3336,73 @@
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" ht="29.25" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B5" s="34"/>
       <c r="C5" s="34"/>
       <c r="D5" s="34"/>
       <c r="E5" s="34"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="132" t="s">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="A6" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="132"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="150"/>
+      <c r="D6" s="150"/>
+      <c r="E6" s="150"/>
       <c r="F6" s="22"/>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="132" t="s">
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="A7" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="132"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
       <c r="I7" s="22"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="132" t="s">
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="A8" s="150" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
+      <c r="B8" s="150"/>
+      <c r="C8" s="150"/>
+      <c r="D8" s="150"/>
+      <c r="E8" s="150"/>
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="132" t="s">
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="A9" s="150" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="132"/>
-      <c r="E9" s="132"/>
+      <c r="B9" s="150"/>
+      <c r="C9" s="150"/>
+      <c r="D9" s="150"/>
+      <c r="E9" s="150"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
       <c r="I9" s="22"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="127" t="s">
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1">
+      <c r="A10" s="147" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
-      <c r="D10" s="127"/>
-      <c r="E10" s="127"/>
+      <c r="B10" s="147"/>
+      <c r="C10" s="147"/>
+      <c r="D10" s="147"/>
+      <c r="E10" s="147"/>
       <c r="F10" s="28"/>
       <c r="I10" s="21"/>
     </row>
@@ -3420,7 +3420,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="10" customFormat="1" ht="19.5" customHeight="1">
@@ -3457,7 +3457,7 @@
         <v>990000.00000000012</v>
       </c>
       <c r="E14" s="123" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F14" s="94"/>
     </row>
@@ -3485,7 +3485,7 @@
         <v>990000.00000000012</v>
       </c>
       <c r="E16" s="123" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F16" s="94"/>
     </row>
@@ -3513,7 +3513,7 @@
         <v>1185800</v>
       </c>
       <c r="E18" s="123" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F18" s="94"/>
     </row>
@@ -3541,7 +3541,7 @@
         <v>1455300.0000000002</v>
       </c>
       <c r="E20" s="123" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F20" s="94"/>
     </row>
@@ -3569,7 +3569,7 @@
         <v>1617000.0000000002</v>
       </c>
       <c r="E22" s="123" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F22" s="94"/>
     </row>
@@ -3597,7 +3597,7 @@
         <v>1940400.0000000002</v>
       </c>
       <c r="E24" s="123" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F24" s="94"/>
     </row>
@@ -3625,7 +3625,7 @@
         <v>2479400</v>
       </c>
       <c r="E26" s="123" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F26" s="94"/>
     </row>
@@ -3640,40 +3640,40 @@
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:6" s="10" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A29" s="133"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="128" t="s">
+      <c r="A29" s="151"/>
+      <c r="B29" s="152"/>
+      <c r="C29" s="148" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="128"/>
-      <c r="E29" s="128"/>
-    </row>
-    <row r="30" spans="1:6" s="5" customFormat="1" ht="18.75">
-      <c r="C30" s="135"/>
-      <c r="D30" s="135"/>
-      <c r="E30" s="135"/>
-    </row>
-    <row r="37" spans="3:5" ht="18.75">
-      <c r="C37" s="139" t="s">
-        <v>184</v>
-      </c>
-      <c r="D37" s="139"/>
-      <c r="E37" s="139"/>
+      <c r="D29" s="148"/>
+      <c r="E29" s="148"/>
+    </row>
+    <row r="30" spans="1:6" s="5" customFormat="1" ht="18">
+      <c r="C30" s="153"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
+    </row>
+    <row r="37" spans="3:5" ht="18">
+      <c r="C37" s="158" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="158"/>
+      <c r="E37" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.5" bottom="0.75" header="0.5" footer="0.3"/>
@@ -3685,28 +3685,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AZ21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" style="66" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="66" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="66" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="66" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="66" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" style="66" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="66" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" style="66" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="66" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="66" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" style="66" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="66" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="66" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="66" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" style="66" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="66" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="66" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="66" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.83203125" style="66" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" style="66" customWidth="1"/>
     <col min="11" max="11" width="9" style="66" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="66" customWidth="1"/>
-    <col min="13" max="14" width="12.140625" style="66" customWidth="1"/>
-    <col min="15" max="15" width="20.7109375" style="66" customWidth="1"/>
-    <col min="16" max="16" width="19.42578125" style="66" customWidth="1"/>
+    <col min="12" max="12" width="12.5" style="66" customWidth="1"/>
+    <col min="13" max="14" width="12.1640625" style="66" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" style="66" customWidth="1"/>
+    <col min="16" max="16" width="19.5" style="66" customWidth="1"/>
     <col min="17" max="17" width="13" style="66" customWidth="1"/>
-    <col min="18" max="18" width="16.42578125" style="66" customWidth="1"/>
-    <col min="19" max="19" width="12.28515625" style="66" customWidth="1"/>
-    <col min="20" max="21" width="11.28515625" style="66" hidden="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="106"/>
+    <col min="18" max="18" width="16.5" style="66" customWidth="1"/>
+    <col min="19" max="19" width="12.33203125" style="66" customWidth="1"/>
+    <col min="20" max="21" width="11.33203125" style="66" hidden="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.1640625" style="106"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="101" customFormat="1" ht="30" customHeight="1">
@@ -3737,7 +3737,7 @@
     <row r="2" spans="1:52" s="101" customFormat="1" ht="21.75" customHeight="1">
       <c r="A2" s="38"/>
       <c r="B2" s="42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C2" s="42"/>
       <c r="D2" s="43"/>
@@ -3808,52 +3808,52 @@
       <c r="U4" s="45"/>
     </row>
     <row r="5" spans="1:52" s="47" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A5" s="143" t="s">
+      <c r="A5" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="143"/>
-      <c r="L5" s="143"/>
-      <c r="M5" s="143"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="143"/>
-      <c r="P5" s="143"/>
-      <c r="Q5" s="143"/>
-      <c r="R5" s="143"/>
-    </row>
-    <row r="6" spans="1:52" s="47" customFormat="1" ht="15.75">
-      <c r="A6" s="144" t="s">
-        <v>193</v>
-      </c>
-      <c r="B6" s="144"/>
-      <c r="C6" s="144"/>
-      <c r="D6" s="144"/>
-      <c r="E6" s="144"/>
-      <c r="F6" s="144"/>
-      <c r="G6" s="144"/>
-      <c r="H6" s="144"/>
-      <c r="I6" s="144"/>
-      <c r="J6" s="144"/>
-      <c r="K6" s="144"/>
-      <c r="L6" s="144"/>
-      <c r="M6" s="144"/>
-      <c r="N6" s="144"/>
-      <c r="O6" s="144"/>
-      <c r="P6" s="144"/>
-      <c r="Q6" s="144"/>
-      <c r="R6" s="144"/>
+      <c r="B5" s="163"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="163"/>
+      <c r="E5" s="163"/>
+      <c r="F5" s="163"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="163"/>
+      <c r="I5" s="163"/>
+      <c r="J5" s="163"/>
+      <c r="K5" s="163"/>
+      <c r="L5" s="163"/>
+      <c r="M5" s="163"/>
+      <c r="N5" s="163"/>
+      <c r="O5" s="163"/>
+      <c r="P5" s="163"/>
+      <c r="Q5" s="163"/>
+      <c r="R5" s="163"/>
+    </row>
+    <row r="6" spans="1:52" s="47" customFormat="1" ht="16">
+      <c r="A6" s="164" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="164"/>
+      <c r="C6" s="164"/>
+      <c r="D6" s="164"/>
+      <c r="E6" s="164"/>
+      <c r="F6" s="164"/>
+      <c r="G6" s="164"/>
+      <c r="H6" s="164"/>
+      <c r="I6" s="164"/>
+      <c r="J6" s="164"/>
+      <c r="K6" s="164"/>
+      <c r="L6" s="164"/>
+      <c r="M6" s="164"/>
+      <c r="N6" s="164"/>
+      <c r="O6" s="164"/>
+      <c r="P6" s="164"/>
+      <c r="Q6" s="164"/>
+      <c r="R6" s="164"/>
     </row>
     <row r="7" spans="1:52" s="102" customFormat="1" ht="27" customHeight="1">
       <c r="A7" s="49" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="49"/>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="8" spans="1:52" s="102" customFormat="1" ht="19.5" customHeight="1">
       <c r="A8" s="44" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="44"/>
@@ -3966,10 +3966,10 @@
         <v>23</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H11" s="54" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I11" s="54" t="s">
         <v>69</v>
@@ -3981,36 +3981,36 @@
         <v>38</v>
       </c>
       <c r="L11" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="M11" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="M11" s="55" t="s">
+      <c r="N11" s="55" t="s">
         <v>175</v>
       </c>
-      <c r="N11" s="55" t="s">
+      <c r="O11" s="55" t="s">
+        <v>195</v>
+      </c>
+      <c r="P11" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q11" s="55" t="s">
         <v>176</v>
       </c>
-      <c r="O11" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="P11" s="55" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q11" s="55" t="s">
+      <c r="R11" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="S11" s="55" t="s">
         <v>177</v>
       </c>
-      <c r="R11" s="55" t="s">
-        <v>195</v>
-      </c>
-      <c r="S11" s="55" t="s">
-        <v>178</v>
-      </c>
       <c r="T11" s="55" t="s">
-        <v>185</v>
-      </c>
-      <c r="U11" s="170" t="s">
-        <v>169</v>
-      </c>
-      <c r="V11" s="171"/>
+        <v>184</v>
+      </c>
+      <c r="U11" s="135" t="s">
+        <v>168</v>
+      </c>
+      <c r="V11" s="136"/>
     </row>
     <row r="12" spans="1:52" s="117" customFormat="1" ht="55.5" customHeight="1" thickBot="1">
       <c r="A12" s="108">
@@ -4071,10 +4071,10 @@
         <f t="shared" ref="Q12" si="0">40000*D12</f>
         <v>40000</v>
       </c>
-      <c r="R12" s="140">
+      <c r="R12" s="160">
         <v>750000</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="160">
         <f>660000*1</f>
         <v>660000</v>
       </c>
@@ -4086,37 +4086,37 @@
         <f>Estimate!AG4</f>
         <v>324000</v>
       </c>
-      <c r="V12" s="178"/>
-      <c r="W12" s="179"/>
-      <c r="X12" s="179"/>
-      <c r="Y12" s="179"/>
-      <c r="Z12" s="179"/>
-      <c r="AA12" s="179"/>
-      <c r="AB12" s="179"/>
-      <c r="AC12" s="179"/>
-      <c r="AD12" s="179"/>
-      <c r="AE12" s="179"/>
-      <c r="AF12" s="179"/>
-      <c r="AG12" s="179"/>
-      <c r="AH12" s="179"/>
-      <c r="AI12" s="179"/>
-      <c r="AJ12" s="179"/>
-      <c r="AK12" s="179"/>
-      <c r="AL12" s="179"/>
-      <c r="AM12" s="179"/>
-      <c r="AN12" s="179"/>
-      <c r="AO12" s="179"/>
-      <c r="AP12" s="179"/>
-      <c r="AQ12" s="179"/>
-      <c r="AR12" s="179"/>
-      <c r="AS12" s="179"/>
-      <c r="AT12" s="179"/>
-      <c r="AU12" s="179"/>
-      <c r="AV12" s="179"/>
-      <c r="AW12" s="179"/>
-      <c r="AX12" s="179"/>
-      <c r="AY12" s="179"/>
-      <c r="AZ12" s="179"/>
+      <c r="V12" s="141"/>
+      <c r="W12" s="142"/>
+      <c r="X12" s="142"/>
+      <c r="Y12" s="142"/>
+      <c r="Z12" s="142"/>
+      <c r="AA12" s="142"/>
+      <c r="AB12" s="142"/>
+      <c r="AC12" s="142"/>
+      <c r="AD12" s="142"/>
+      <c r="AE12" s="142"/>
+      <c r="AF12" s="142"/>
+      <c r="AG12" s="142"/>
+      <c r="AH12" s="142"/>
+      <c r="AI12" s="142"/>
+      <c r="AJ12" s="142"/>
+      <c r="AK12" s="142"/>
+      <c r="AL12" s="142"/>
+      <c r="AM12" s="142"/>
+      <c r="AN12" s="142"/>
+      <c r="AO12" s="142"/>
+      <c r="AP12" s="142"/>
+      <c r="AQ12" s="142"/>
+      <c r="AR12" s="142"/>
+      <c r="AS12" s="142"/>
+      <c r="AT12" s="142"/>
+      <c r="AU12" s="142"/>
+      <c r="AV12" s="142"/>
+      <c r="AW12" s="142"/>
+      <c r="AX12" s="142"/>
+      <c r="AY12" s="142"/>
+      <c r="AZ12" s="142"/>
     </row>
     <row r="13" spans="1:52" s="117" customFormat="1" ht="55.5" customHeight="1" thickBot="1">
       <c r="A13" s="108">
@@ -4177,8 +4177,8 @@
         <f t="shared" ref="Q13:Q15" si="4">40000*D13</f>
         <v>40000</v>
       </c>
-      <c r="R13" s="141"/>
-      <c r="S13" s="141"/>
+      <c r="R13" s="161"/>
+      <c r="S13" s="161"/>
       <c r="T13" s="115">
         <f>Estimate!AE5</f>
         <v>78000</v>
@@ -4187,37 +4187,37 @@
         <f>Estimate!AG5</f>
         <v>324000</v>
       </c>
-      <c r="V13" s="178"/>
-      <c r="W13" s="179"/>
-      <c r="X13" s="179"/>
-      <c r="Y13" s="179"/>
-      <c r="Z13" s="179"/>
-      <c r="AA13" s="179"/>
-      <c r="AB13" s="179"/>
-      <c r="AC13" s="179"/>
-      <c r="AD13" s="179"/>
-      <c r="AE13" s="179"/>
-      <c r="AF13" s="179"/>
-      <c r="AG13" s="179"/>
-      <c r="AH13" s="179"/>
-      <c r="AI13" s="179"/>
-      <c r="AJ13" s="179"/>
-      <c r="AK13" s="179"/>
-      <c r="AL13" s="179"/>
-      <c r="AM13" s="179"/>
-      <c r="AN13" s="179"/>
-      <c r="AO13" s="179"/>
-      <c r="AP13" s="179"/>
-      <c r="AQ13" s="179"/>
-      <c r="AR13" s="179"/>
-      <c r="AS13" s="179"/>
-      <c r="AT13" s="179"/>
-      <c r="AU13" s="179"/>
-      <c r="AV13" s="179"/>
-      <c r="AW13" s="179"/>
-      <c r="AX13" s="179"/>
-      <c r="AY13" s="179"/>
-      <c r="AZ13" s="179"/>
+      <c r="V13" s="141"/>
+      <c r="W13" s="142"/>
+      <c r="X13" s="142"/>
+      <c r="Y13" s="142"/>
+      <c r="Z13" s="142"/>
+      <c r="AA13" s="142"/>
+      <c r="AB13" s="142"/>
+      <c r="AC13" s="142"/>
+      <c r="AD13" s="142"/>
+      <c r="AE13" s="142"/>
+      <c r="AF13" s="142"/>
+      <c r="AG13" s="142"/>
+      <c r="AH13" s="142"/>
+      <c r="AI13" s="142"/>
+      <c r="AJ13" s="142"/>
+      <c r="AK13" s="142"/>
+      <c r="AL13" s="142"/>
+      <c r="AM13" s="142"/>
+      <c r="AN13" s="142"/>
+      <c r="AO13" s="142"/>
+      <c r="AP13" s="142"/>
+      <c r="AQ13" s="142"/>
+      <c r="AR13" s="142"/>
+      <c r="AS13" s="142"/>
+      <c r="AT13" s="142"/>
+      <c r="AU13" s="142"/>
+      <c r="AV13" s="142"/>
+      <c r="AW13" s="142"/>
+      <c r="AX13" s="142"/>
+      <c r="AY13" s="142"/>
+      <c r="AZ13" s="142"/>
     </row>
     <row r="14" spans="1:52" s="117" customFormat="1" ht="55.5" customHeight="1" thickBot="1">
       <c r="A14" s="108">
@@ -4278,8 +4278,8 @@
         <f t="shared" ref="Q14" si="6">40000*D14</f>
         <v>40000</v>
       </c>
-      <c r="R14" s="141"/>
-      <c r="S14" s="141"/>
+      <c r="R14" s="161"/>
+      <c r="S14" s="161"/>
       <c r="T14" s="115">
         <f>Estimate!AE6</f>
         <v>78000</v>
@@ -4288,73 +4288,73 @@
         <f>Estimate!AG6</f>
         <v>324000</v>
       </c>
-      <c r="V14" s="178"/>
-      <c r="W14" s="179"/>
-      <c r="X14" s="179"/>
-      <c r="Y14" s="179"/>
-      <c r="Z14" s="179"/>
-      <c r="AA14" s="179"/>
-      <c r="AB14" s="179"/>
-      <c r="AC14" s="179"/>
-      <c r="AD14" s="179"/>
-      <c r="AE14" s="179"/>
-      <c r="AF14" s="179"/>
-      <c r="AG14" s="179"/>
-      <c r="AH14" s="179"/>
-      <c r="AI14" s="179"/>
-      <c r="AJ14" s="179"/>
-      <c r="AK14" s="179"/>
-      <c r="AL14" s="179"/>
-      <c r="AM14" s="179"/>
-      <c r="AN14" s="179"/>
-      <c r="AO14" s="179"/>
-      <c r="AP14" s="179"/>
-      <c r="AQ14" s="179"/>
-      <c r="AR14" s="179"/>
-      <c r="AS14" s="179"/>
-      <c r="AT14" s="179"/>
-      <c r="AU14" s="179"/>
-      <c r="AV14" s="179"/>
-      <c r="AW14" s="179"/>
-      <c r="AX14" s="179"/>
-      <c r="AY14" s="179"/>
-      <c r="AZ14" s="179"/>
+      <c r="V14" s="141"/>
+      <c r="W14" s="142"/>
+      <c r="X14" s="142"/>
+      <c r="Y14" s="142"/>
+      <c r="Z14" s="142"/>
+      <c r="AA14" s="142"/>
+      <c r="AB14" s="142"/>
+      <c r="AC14" s="142"/>
+      <c r="AD14" s="142"/>
+      <c r="AE14" s="142"/>
+      <c r="AF14" s="142"/>
+      <c r="AG14" s="142"/>
+      <c r="AH14" s="142"/>
+      <c r="AI14" s="142"/>
+      <c r="AJ14" s="142"/>
+      <c r="AK14" s="142"/>
+      <c r="AL14" s="142"/>
+      <c r="AM14" s="142"/>
+      <c r="AN14" s="142"/>
+      <c r="AO14" s="142"/>
+      <c r="AP14" s="142"/>
+      <c r="AQ14" s="142"/>
+      <c r="AR14" s="142"/>
+      <c r="AS14" s="142"/>
+      <c r="AT14" s="142"/>
+      <c r="AU14" s="142"/>
+      <c r="AV14" s="142"/>
+      <c r="AW14" s="142"/>
+      <c r="AX14" s="142"/>
+      <c r="AY14" s="142"/>
+      <c r="AZ14" s="142"/>
     </row>
     <row r="15" spans="1:52" s="117" customFormat="1" ht="55.5" customHeight="1" thickBot="1">
-      <c r="A15" s="159">
+      <c r="A15" s="126">
         <v>4</v>
       </c>
-      <c r="B15" s="160">
+      <c r="B15" s="127">
         <f>Estimate!B7</f>
         <v>1500063105</v>
       </c>
-      <c r="C15" s="161" t="str">
+      <c r="C15" s="128" t="str">
         <f>+Estimate!C7</f>
         <v>Set Camera Tester</v>
       </c>
-      <c r="D15" s="162">
+      <c r="D15" s="129">
         <f>Estimate!H7</f>
         <v>1</v>
       </c>
-      <c r="E15" s="162">
+      <c r="E15" s="129">
         <f>Estimate!G7</f>
         <v>140</v>
       </c>
-      <c r="F15" s="162">
+      <c r="F15" s="129">
         <f>Estimate!P7</f>
         <v>140</v>
       </c>
-      <c r="G15" s="163">
+      <c r="G15" s="130">
         <f>Estimate!O7</f>
         <v>2.16</v>
       </c>
-      <c r="H15" s="163">
+      <c r="H15" s="130">
         <f>Estimate!L7*Estimate!M7</f>
         <v>1.2</v>
       </c>
-      <c r="I15" s="164"/>
-      <c r="J15" s="165"/>
-      <c r="K15" s="162"/>
+      <c r="I15" s="131"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="129"/>
       <c r="L15" s="115">
         <f>Estimate!AC7</f>
         <v>1436400</v>
@@ -4379,8 +4379,8 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="R15" s="169"/>
-      <c r="S15" s="141"/>
+      <c r="R15" s="167"/>
+      <c r="S15" s="161"/>
       <c r="T15" s="115">
         <f>Estimate!AE7</f>
         <v>78000</v>
@@ -4389,105 +4389,105 @@
         <f>Estimate!AG7</f>
         <v>324000</v>
       </c>
-      <c r="V15" s="178"/>
-      <c r="W15" s="179"/>
-      <c r="X15" s="179"/>
-      <c r="Y15" s="179"/>
-      <c r="Z15" s="179"/>
-      <c r="AA15" s="179"/>
-      <c r="AB15" s="179"/>
-      <c r="AC15" s="179"/>
-      <c r="AD15" s="179"/>
-      <c r="AE15" s="179"/>
-      <c r="AF15" s="179"/>
-      <c r="AG15" s="179"/>
-      <c r="AH15" s="179"/>
-      <c r="AI15" s="179"/>
-      <c r="AJ15" s="179"/>
-      <c r="AK15" s="179"/>
-      <c r="AL15" s="179"/>
-      <c r="AM15" s="179"/>
-      <c r="AN15" s="179"/>
-      <c r="AO15" s="179"/>
-      <c r="AP15" s="179"/>
-      <c r="AQ15" s="179"/>
-      <c r="AR15" s="179"/>
-      <c r="AS15" s="179"/>
-      <c r="AT15" s="179"/>
-      <c r="AU15" s="179"/>
-      <c r="AV15" s="179"/>
-      <c r="AW15" s="179"/>
-      <c r="AX15" s="179"/>
-      <c r="AY15" s="179"/>
-      <c r="AZ15" s="179"/>
+      <c r="V15" s="141"/>
+      <c r="W15" s="142"/>
+      <c r="X15" s="142"/>
+      <c r="Y15" s="142"/>
+      <c r="Z15" s="142"/>
+      <c r="AA15" s="142"/>
+      <c r="AB15" s="142"/>
+      <c r="AC15" s="142"/>
+      <c r="AD15" s="142"/>
+      <c r="AE15" s="142"/>
+      <c r="AF15" s="142"/>
+      <c r="AG15" s="142"/>
+      <c r="AH15" s="142"/>
+      <c r="AI15" s="142"/>
+      <c r="AJ15" s="142"/>
+      <c r="AK15" s="142"/>
+      <c r="AL15" s="142"/>
+      <c r="AM15" s="142"/>
+      <c r="AN15" s="142"/>
+      <c r="AO15" s="142"/>
+      <c r="AP15" s="142"/>
+      <c r="AQ15" s="142"/>
+      <c r="AR15" s="142"/>
+      <c r="AS15" s="142"/>
+      <c r="AT15" s="142"/>
+      <c r="AU15" s="142"/>
+      <c r="AV15" s="142"/>
+      <c r="AW15" s="142"/>
+      <c r="AX15" s="142"/>
+      <c r="AY15" s="142"/>
+      <c r="AZ15" s="142"/>
     </row>
     <row r="16" spans="1:52" s="103" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="166" t="s">
+      <c r="A16" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="166"/>
-      <c r="C16" s="167"/>
-      <c r="D16" s="168">
+      <c r="B16" s="165"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="134">
         <f t="shared" ref="D16:U16" si="7">SUM(D12:D15)</f>
         <v>4</v>
       </c>
-      <c r="E16" s="168">
+      <c r="E16" s="134">
         <f t="shared" si="7"/>
         <v>560</v>
       </c>
-      <c r="F16" s="168">
+      <c r="F16" s="134">
         <f t="shared" si="7"/>
         <v>560</v>
       </c>
-      <c r="G16" s="180">
+      <c r="G16" s="143">
         <f t="shared" si="7"/>
         <v>8.64</v>
       </c>
-      <c r="H16" s="180">
+      <c r="H16" s="143">
         <f t="shared" si="7"/>
         <v>4.8</v>
       </c>
-      <c r="I16" s="168">
+      <c r="I16" s="134">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J16" s="168">
+      <c r="J16" s="134">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K16" s="168">
+      <c r="K16" s="134">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L16" s="176">
+      <c r="L16" s="139">
         <f t="shared" si="7"/>
         <v>5745600</v>
       </c>
-      <c r="M16" s="177">
+      <c r="M16" s="140">
         <f t="shared" si="7"/>
         <v>7776000.0000000009</v>
       </c>
-      <c r="N16" s="176">
+      <c r="N16" s="139">
         <f t="shared" si="7"/>
         <v>80000</v>
       </c>
-      <c r="O16" s="176">
+      <c r="O16" s="139">
         <f t="shared" si="7"/>
         <v>140000</v>
       </c>
-      <c r="P16" s="176">
+      <c r="P16" s="139">
         <f t="shared" si="7"/>
         <v>140000</v>
       </c>
-      <c r="Q16" s="176">
+      <c r="Q16" s="139">
         <f t="shared" si="7"/>
         <v>160000</v>
       </c>
-      <c r="R16" s="176">
+      <c r="R16" s="139">
         <f t="shared" si="7"/>
         <v>750000</v>
       </c>
-      <c r="S16" s="176">
+      <c r="S16" s="139">
         <f>SUM(S12:S15)</f>
         <v>660000</v>
       </c>
@@ -4508,12 +4508,12 @@
       <c r="C17" s="56"/>
       <c r="D17" s="63"/>
       <c r="E17" s="56"/>
-      <c r="F17" s="145">
+      <c r="F17" s="166">
         <f>SUM(L16:S16)</f>
         <v>15451600</v>
       </c>
-      <c r="G17" s="145"/>
-      <c r="H17" s="145"/>
+      <c r="G17" s="166"/>
+      <c r="H17" s="166"/>
       <c r="I17" s="57" t="s">
         <v>41</v>
       </c>
@@ -4530,7 +4530,7 @@
       <c r="T17" s="59"/>
       <c r="U17" s="59"/>
     </row>
-    <row r="18" spans="1:21" s="104" customFormat="1" ht="15.75" hidden="1">
+    <row r="18" spans="1:21" s="104" customFormat="1" ht="16" hidden="1">
       <c r="A18" s="60"/>
       <c r="B18" s="56"/>
       <c r="C18" s="56"/>
@@ -4553,15 +4553,15 @@
       <c r="T18" s="62"/>
       <c r="U18" s="62"/>
     </row>
-    <row r="19" spans="1:21" s="105" customFormat="1" ht="15.75" hidden="1">
+    <row r="19" spans="1:21" s="105" customFormat="1" ht="16" hidden="1">
       <c r="A19" s="63"/>
       <c r="B19" s="63"/>
       <c r="C19" s="63"/>
       <c r="D19" s="63"/>
       <c r="E19" s="63"/>
-      <c r="F19" s="142"/>
-      <c r="G19" s="142"/>
-      <c r="H19" s="142"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="162"/>
+      <c r="H19" s="162"/>
       <c r="I19" s="63"/>
       <c r="J19" s="62"/>
       <c r="K19" s="62"/>
@@ -4576,7 +4576,7 @@
       <c r="T19" s="62"/>
       <c r="U19" s="62"/>
     </row>
-    <row r="20" spans="1:21" s="105" customFormat="1" ht="15.75">
+    <row r="20" spans="1:21" s="105" customFormat="1" ht="16">
       <c r="A20" s="63"/>
       <c r="B20" s="63"/>
       <c r="C20" s="63"/>
@@ -4603,10 +4603,10 @@
       <c r="F21" s="67"/>
       <c r="G21" s="67"/>
       <c r="H21" s="67"/>
-      <c r="J21" s="172" t="s">
-        <v>191</v>
-      </c>
-      <c r="K21" s="172"/>
+      <c r="J21" s="159" t="s">
+        <v>190</v>
+      </c>
+      <c r="K21" s="159"/>
       <c r="L21" s="67"/>
       <c r="M21" s="67"/>
       <c r="N21" s="67"/>
@@ -4644,36 +4644,36 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AG11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="10.28515625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="9"/>
-    <col min="16" max="16" width="11.28515625" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" customWidth="1"/>
-    <col min="20" max="20" width="11.140625" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="15.28515625" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="11.28515625" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="13.85546875" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5" customWidth="1"/>
+    <col min="19" max="19" width="16.5" customWidth="1"/>
+    <col min="20" max="20" width="11.1640625" customWidth="1"/>
+    <col min="21" max="21" width="14.5" customWidth="1"/>
+    <col min="22" max="22" width="12.83203125" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="15.33203125" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="11.33203125" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="13.83203125" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="12.83203125" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="14.33203125" hidden="1" customWidth="1"/>
     <col min="28" max="28" width="13" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" customWidth="1"/>
-    <col min="30" max="30" width="17.7109375" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="17.7109375" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="14.33203125" customWidth="1"/>
+    <col min="30" max="30" width="17.6640625" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="15.83203125" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="17.6640625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="15.83203125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="21" customFormat="1" ht="31.5">
+    <row r="1" spans="1:33" s="21" customFormat="1" ht="34">
       <c r="A1" s="68"/>
       <c r="B1" s="68"/>
       <c r="C1" s="68"/>
@@ -4690,76 +4690,76 @@
       <c r="L1" s="69"/>
     </row>
     <row r="2" spans="1:33" s="21" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A2" s="146" t="s">
+      <c r="A2" s="168" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="147" t="s">
+      <c r="B2" s="169" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="147" t="s">
+      <c r="C2" s="169" t="s">
         <v>145</v>
       </c>
-      <c r="D2" s="148" t="s">
+      <c r="D2" s="170" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="148"/>
-      <c r="F2" s="148"/>
-      <c r="G2" s="148"/>
-      <c r="H2" s="146" t="s">
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="168" t="s">
         <v>44</v>
       </c>
       <c r="I2" s="70"/>
-      <c r="J2" s="146" t="s">
+      <c r="J2" s="168" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="146" t="s">
+      <c r="K2" s="168" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="148" t="s">
+      <c r="L2" s="170" t="s">
         <v>47</v>
       </c>
-      <c r="M2" s="148"/>
-      <c r="N2" s="148"/>
-      <c r="O2" s="148"/>
-      <c r="P2" s="148"/>
-      <c r="Q2" s="148"/>
-      <c r="R2" s="148"/>
-      <c r="S2" s="148"/>
-      <c r="T2" s="146" t="s">
+      <c r="M2" s="170"/>
+      <c r="N2" s="170"/>
+      <c r="O2" s="170"/>
+      <c r="P2" s="170"/>
+      <c r="Q2" s="170"/>
+      <c r="R2" s="170"/>
+      <c r="S2" s="170"/>
+      <c r="T2" s="168" t="s">
         <v>48</v>
       </c>
-      <c r="U2" s="146"/>
-      <c r="V2" s="146" t="s">
+      <c r="U2" s="168"/>
+      <c r="V2" s="168" t="s">
         <v>49</v>
       </c>
-      <c r="W2" s="146"/>
-      <c r="X2" s="146" t="s">
+      <c r="W2" s="168"/>
+      <c r="X2" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="Y2" s="146"/>
-      <c r="Z2" s="146" t="s">
+      <c r="Y2" s="168"/>
+      <c r="Z2" s="168" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="146"/>
-      <c r="AB2" s="146" t="s">
-        <v>162</v>
-      </c>
-      <c r="AC2" s="146"/>
-      <c r="AD2" s="146" t="s">
+      <c r="AA2" s="168"/>
+      <c r="AB2" s="168" t="s">
+        <v>161</v>
+      </c>
+      <c r="AC2" s="168"/>
+      <c r="AD2" s="168" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE2" s="168"/>
+      <c r="AF2" s="168" t="s">
         <v>180</v>
       </c>
-      <c r="AE2" s="146"/>
-      <c r="AF2" s="146" t="s">
-        <v>181</v>
-      </c>
-      <c r="AG2" s="146"/>
-    </row>
-    <row r="3" spans="1:33" s="21" customFormat="1" ht="31.5">
-      <c r="A3" s="146" t="s">
+      <c r="AG2" s="168"/>
+    </row>
+    <row r="3" spans="1:33" s="21" customFormat="1" ht="34">
+      <c r="A3" s="168" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="169"/>
       <c r="D3" s="70" t="s">
         <v>53</v>
       </c>
@@ -4772,12 +4772,12 @@
       <c r="G3" s="70" t="s">
         <v>134</v>
       </c>
-      <c r="H3" s="146"/>
+      <c r="H3" s="168"/>
       <c r="I3" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="J3" s="146"/>
-      <c r="K3" s="146"/>
+        <v>163</v>
+      </c>
+      <c r="J3" s="168"/>
+      <c r="K3" s="168"/>
       <c r="L3" s="70" t="s">
         <v>53</v>
       </c>
@@ -4794,10 +4794,10 @@
         <v>54</v>
       </c>
       <c r="Q3" s="70" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R3" s="70" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S3" s="70" t="s">
         <v>46</v>
@@ -4853,7 +4853,7 @@
         <v>1500064205</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D4" s="118">
         <v>0.9</v>
@@ -4966,7 +4966,7 @@
         <v>1500067875</v>
       </c>
       <c r="C5" s="118" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D5" s="118">
         <v>0.9</v>
@@ -5079,7 +5079,7 @@
         <v>1500063106</v>
       </c>
       <c r="C6" s="118" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D6" s="118">
         <v>0.9</v>
@@ -5192,7 +5192,7 @@
         <v>1500063105</v>
       </c>
       <c r="C7" s="118" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D7" s="118">
         <v>0.9</v>
@@ -5297,7 +5297,7 @@
         <v>324000</v>
       </c>
     </row>
-    <row r="8" spans="1:33" s="73" customFormat="1" ht="15.75">
+    <row r="8" spans="1:33" s="73" customFormat="1" ht="17">
       <c r="A8" s="71"/>
       <c r="B8" s="72" t="s">
         <v>57</v>
@@ -5327,35 +5327,35 @@
         <v>0.94500000000000006</v>
       </c>
       <c r="L8" s="71">
-        <f>SUM(L4:L7)</f>
+        <f t="shared" ref="L8:S8" si="34">SUM(L4:L7)</f>
         <v>4.8</v>
       </c>
       <c r="M8" s="71">
-        <f>SUM(M4:M7)</f>
+        <f t="shared" si="34"/>
         <v>4</v>
       </c>
       <c r="N8" s="71">
-        <f>SUM(N4:N7)</f>
+        <f t="shared" si="34"/>
         <v>7.2</v>
       </c>
       <c r="O8" s="98">
-        <f>SUM(O4:O7)</f>
+        <f t="shared" si="34"/>
         <v>8.64</v>
       </c>
       <c r="P8" s="98">
-        <f>SUM(P4:P7)</f>
+        <f t="shared" si="34"/>
         <v>560</v>
       </c>
       <c r="Q8" s="98">
-        <f>SUM(Q4:Q7)</f>
+        <f t="shared" si="34"/>
         <v>4</v>
       </c>
       <c r="R8" s="98">
-        <f>SUM(R4:R7)</f>
+        <f t="shared" si="34"/>
         <v>560</v>
       </c>
       <c r="S8" s="71">
-        <f>SUM(S4:S7)</f>
+        <f t="shared" si="34"/>
         <v>8.64</v>
       </c>
       <c r="T8" s="98"/>
@@ -5364,27 +5364,27 @@
         <v>7776000.0000000009</v>
       </c>
       <c r="V8" s="99">
-        <f t="shared" ref="V8:AA8" si="34">SUM(V4:V4)</f>
+        <f t="shared" ref="V8:AA8" si="35">SUM(V4:V4)</f>
         <v>0</v>
       </c>
       <c r="W8" s="99" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#REF!</v>
       </c>
       <c r="X8" s="99">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Y8" s="99">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z8" s="99">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AA8" s="99" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#REF!</v>
       </c>
       <c r="AB8" s="99"/>
@@ -5403,7 +5403,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="15.75">
+    <row r="9" spans="1:33" ht="16">
       <c r="I9" s="107"/>
     </row>
     <row r="11" spans="1:33">
@@ -5438,95 +5438,95 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="24.85546875" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" thickBot="1">
+    <row r="1" spans="1:17" ht="16" thickBot="1">
       <c r="A1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="47.25">
-      <c r="A2" s="151" t="s">
+    <row r="2" spans="1:17" ht="51">
+      <c r="A2" s="171" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="153" t="s">
+      <c r="B2" s="173" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="155" t="s">
+      <c r="E2" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="155" t="s">
+      <c r="F2" s="175" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="175" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="175" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="157" t="s">
+      <c r="I2" s="177" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="155" t="s">
+      <c r="J2" s="175" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="155" t="s">
+      <c r="K2" s="175" t="s">
         <v>82</v>
       </c>
-      <c r="L2" s="155" t="s">
+      <c r="L2" s="175" t="s">
         <v>83</v>
       </c>
       <c r="M2" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="N2" s="149" t="s">
+      <c r="N2" s="179" t="s">
         <v>86</v>
       </c>
-      <c r="O2" s="149" t="s">
+      <c r="O2" s="179" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="149" t="s">
+      <c r="P2" s="179" t="s">
         <v>88</v>
       </c>
-      <c r="Q2" s="149" t="s">
+      <c r="Q2" s="179" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="35.25" thickBot="1">
-      <c r="A3" s="152"/>
-      <c r="B3" s="154"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
-      <c r="L3" s="156"/>
+    <row r="3" spans="1:17" ht="39" thickBot="1">
+      <c r="A3" s="172"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="176"/>
+      <c r="D3" s="176"/>
+      <c r="E3" s="176"/>
+      <c r="F3" s="176"/>
+      <c r="G3" s="176"/>
+      <c r="H3" s="176"/>
+      <c r="I3" s="178"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="176"/>
+      <c r="L3" s="176"/>
       <c r="M3" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="N3" s="150"/>
-      <c r="O3" s="150"/>
-      <c r="P3" s="150"/>
-      <c r="Q3" s="150"/>
-    </row>
-    <row r="4" spans="1:17" ht="18.75" thickTop="1" thickBot="1">
+      <c r="N3" s="180"/>
+      <c r="O3" s="180"/>
+      <c r="P3" s="180"/>
+      <c r="Q3" s="180"/>
+    </row>
+    <row r="4" spans="1:17" ht="20" thickTop="1" thickBot="1">
       <c r="A4" s="78" t="s">
         <v>90</v>
       </c>
@@ -5579,7 +5579,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="16.5" thickBot="1">
+    <row r="5" spans="1:17" ht="17" thickBot="1">
       <c r="A5" s="78" t="s">
         <v>90</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="18" thickBot="1">
+    <row r="6" spans="1:17" ht="19" thickBot="1">
       <c r="A6" s="78" t="s">
         <v>90</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="18" thickBot="1">
+    <row r="7" spans="1:17" ht="19" thickBot="1">
       <c r="A7" s="78" t="s">
         <v>90</v>
       </c>
@@ -5738,84 +5738,84 @@
         <v>950</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="16.5" thickBot="1">
+    <row r="10" spans="1:17" ht="17" thickBot="1">
       <c r="A10" s="89" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="47.25">
-      <c r="A11" s="151" t="s">
+    <row r="11" spans="1:17" ht="51">
+      <c r="A11" s="171" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="153" t="s">
+      <c r="B11" s="173" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155" t="s">
+      <c r="C11" s="175"/>
+      <c r="D11" s="175" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="155" t="s">
+      <c r="E11" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="F11" s="155" t="s">
+      <c r="F11" s="175" t="s">
         <v>77</v>
       </c>
-      <c r="G11" s="155" t="s">
+      <c r="G11" s="175" t="s">
         <v>78</v>
       </c>
-      <c r="H11" s="155" t="s">
+      <c r="H11" s="175" t="s">
         <v>79</v>
       </c>
-      <c r="I11" s="157" t="s">
+      <c r="I11" s="177" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="155" t="s">
+      <c r="J11" s="175" t="s">
         <v>81</v>
       </c>
-      <c r="K11" s="155" t="s">
+      <c r="K11" s="175" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="155" t="s">
+      <c r="L11" s="175" t="s">
         <v>83</v>
       </c>
       <c r="M11" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="N11" s="149" t="s">
+      <c r="N11" s="179" t="s">
         <v>86</v>
       </c>
-      <c r="O11" s="149" t="s">
+      <c r="O11" s="179" t="s">
         <v>87</v>
       </c>
-      <c r="P11" s="149" t="s">
+      <c r="P11" s="179" t="s">
         <v>88</v>
       </c>
-      <c r="Q11" s="149" t="s">
+      <c r="Q11" s="179" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="35.25" thickBot="1">
-      <c r="A12" s="152"/>
-      <c r="B12" s="154"/>
-      <c r="C12" s="156"/>
-      <c r="D12" s="156"/>
-      <c r="E12" s="156"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="158"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="156"/>
-      <c r="L12" s="156"/>
+    <row r="12" spans="1:17" ht="39" thickBot="1">
+      <c r="A12" s="172"/>
+      <c r="B12" s="174"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="176"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="178"/>
+      <c r="J12" s="176"/>
+      <c r="K12" s="176"/>
+      <c r="L12" s="176"/>
       <c r="M12" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="N12" s="150"/>
-      <c r="O12" s="150"/>
-      <c r="P12" s="150"/>
-      <c r="Q12" s="150"/>
-    </row>
-    <row r="13" spans="1:17" ht="18.75" thickTop="1" thickBot="1">
+      <c r="N12" s="180"/>
+      <c r="O12" s="180"/>
+      <c r="P12" s="180"/>
+      <c r="Q12" s="180"/>
+    </row>
+    <row r="13" spans="1:17" ht="20" thickTop="1" thickBot="1">
       <c r="A13" s="83" t="s">
         <v>90</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="18" thickBot="1">
+    <row r="14" spans="1:17" ht="19" thickBot="1">
       <c r="A14" s="83" t="s">
         <v>90</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="18" thickBot="1">
+    <row r="15" spans="1:17" ht="19" thickBot="1">
       <c r="A15" s="83" t="s">
         <v>90</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="18" thickBot="1">
+    <row r="16" spans="1:17" ht="19" thickBot="1">
       <c r="A16" s="83" t="s">
         <v>90</v>
       </c>
@@ -6027,7 +6027,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="18" thickBot="1">
+    <row r="17" spans="1:17" ht="19" thickBot="1">
       <c r="A17" s="83" t="s">
         <v>90</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="18" thickBot="1">
+    <row r="18" spans="1:17" ht="19" thickBot="1">
       <c r="A18" s="83" t="s">
         <v>90</v>
       </c>
@@ -6133,30 +6133,14 @@
         <v>950</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" ht="16">
       <c r="A20" s="88"/>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" ht="16">
       <c r="A22" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
     <mergeCell ref="P11:P12"/>
     <mergeCell ref="Q11:Q12"/>
     <mergeCell ref="P2:P3"/>
@@ -6173,6 +6157,22 @@
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="L11:L12"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6182,9 +6182,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A6:F9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="6" spans="1:6">
